--- a/data/trans_orig/P32D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50509</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33310</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>59676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281600</t>
+          <t>285201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307789</t>
+          <t>308898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141202</t>
+          <t>141834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152585</t>
+          <t>152859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429815</t>
+          <t>431343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>457709</t>
+          <t>458123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46574</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71227</t>
+          <t>72020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427342</t>
+          <t>427733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452618</t>
+          <t>452057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169901</t>
+          <t>169461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187216</t>
+          <t>186657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>604295</t>
+          <t>603502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>636334</t>
+          <t>634677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289808</t>
+          <t>289359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309991</t>
+          <t>310196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>359345</t>
+          <t>359679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>375280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654845</t>
+          <t>654970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>689566</t>
+          <t>690948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68797</t>
+          <t>71447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55666</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90964</t>
+          <t>90797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>370487</t>
+          <t>367837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>399689</t>
+          <t>397378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258705</t>
+          <t>259278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277497</t>
+          <t>277836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636738</t>
+          <t>636905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672036</t>
+          <t>670798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171136</t>
+          <t>171466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76684</t>
+          <t>76004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149926</t>
+          <t>147196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231208</t>
+          <t>231696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1399908</t>
+          <t>1399578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1448393</t>
+          <t>1448813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>947684</t>
+          <t>948364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>996272</t>
+          <t>996798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2364205</t>
+          <t>2363717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2445487</t>
+          <t>2448217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>51211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44959</t>
+          <t>46075</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59676</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>297961</t>
+          <t>317379</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285201</t>
+          <t>301147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308898</t>
+          <t>328461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>148100</t>
+          <t>160825</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141834</t>
+          <t>153604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152859</t>
+          <t>165675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>446060</t>
+          <t>478204</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431343</t>
+          <t>461717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>458123</t>
+          <t>490701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332109</t>
+          <t>352358</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332109</t>
+          <t>352358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>332109</t>
+          <t>352358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>158911</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158911</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158911</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>524279</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>524279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>524279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>38849</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46183</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32145</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53590</t>
+          <t>64042</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40845</t>
+          <t>47726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72020</t>
+          <t>83445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>441922</t>
+          <t>459659</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427733</t>
+          <t>442531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452057</t>
+          <t>471014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>180010</t>
+          <t>198694</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169461</t>
+          <t>188475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>186657</t>
+          <t>206897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>621932</t>
+          <t>658353</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>603502</t>
+          <t>638950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>634677</t>
+          <t>674669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>498508</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>498508</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>498508</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>675522</t>
+          <t>722395</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>675522</t>
+          <t>722395</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>675522</t>
+          <t>722395</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>36385</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46199</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>301786</t>
+          <t>330282</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289359</t>
+          <t>316351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310196</t>
+          <t>339582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>370679</t>
+          <t>194177</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>359679</t>
+          <t>185608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375280</t>
+          <t>198077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>672465</t>
+          <t>524459</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654970</t>
+          <t>508895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>690948</t>
+          <t>535748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325735</t>
+          <t>360418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>325735</t>
+          <t>360418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>325735</t>
+          <t>360418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>560844</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>560844</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>560844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54018</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41906</t>
+          <t>44636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71447</t>
+          <t>76145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>34586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71572</t>
+          <t>79167</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56904</t>
+          <t>63050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90797</t>
+          <t>101500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>385266</t>
+          <t>403796</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367837</t>
+          <t>385169</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>397378</t>
+          <t>416678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>270865</t>
+          <t>286283</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259278</t>
+          <t>273345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277836</t>
+          <t>294869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>656130</t>
+          <t>690078</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636905</t>
+          <t>667745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>670798</t>
+          <t>706195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>727702</t>
+          <t>769245</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>727702</t>
+          <t>769245</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>727702</t>
+          <t>769245</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,69 +2097,69 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>135843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171466</t>
+          <t>191270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>64186</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50900</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>82942</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54715</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27570</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76004</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>213</t>
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>225668</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147196</t>
+          <t>197117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231696</t>
+          <t>259529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -2210,67 +2210,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1426934</t>
+          <t>1511115</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1399578</t>
+          <t>1481327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1448813</t>
+          <t>1536754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>839979</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>821223</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>853265</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>90,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1132</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>969653</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>948364</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>996798</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,66%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2396589</t>
+          <t>2351094</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2363717</t>
+          <t>2317233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2448217</t>
+          <t>2379645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
